--- a/dcf/JPM.xlsx
+++ b/dcf/JPM.xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1099,25 +1099,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.05624403911248081</v>
+        <v>0.05637883953124738</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.06124403911248081</v>
+        <v>0.06137883953124738</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.06624403911248081</v>
+        <v>0.06637883953124737</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.07124403911248081</v>
+        <v>0.07137883953124738</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.07624403911248082</v>
+        <v>0.07637883953124738</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.08124403911248081</v>
+        <v>0.08137883953124737</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.08624403911248081</v>
+        <v>0.08637883953124738</v>
       </c>
     </row>
     <row r="5">
@@ -1125,25 +1125,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="8" t="n">
-        <v>933.9135678764613</v>
+        <v>933.4945447161103</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>918.7220545574205</v>
+        <v>918.322295356052</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>904.2267158949059</v>
+        <v>903.8452133908602</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>890.3912472167408</v>
+        <v>890.0270520575549</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>877.1814259888554</v>
+        <v>876.8336431265087</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>864.5649825072483</v>
+        <v>864.2327678341293</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>852.5114792050994</v>
+        <v>852.1940364135439</v>
       </c>
     </row>
     <row r="6">
@@ -1151,25 +1151,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>958.8590696351549</v>
+        <v>958.408232757224</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>942.5168686170598</v>
+        <v>942.0869060781691</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>926.9289601413573</v>
+        <v>926.5187761622949</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>912.0558520051271</v>
+        <v>911.6644139627467</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>897.8603226707069</v>
+        <v>897.4866571597685</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>884.307280004018</v>
+        <v>883.9504691623453</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>871.363629436431</v>
+        <v>871.0228075146096</v>
       </c>
     </row>
     <row r="7">
@@ -1177,25 +1177,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>983.8045713938485</v>
+        <v>983.3219207983377</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>966.3116826766993</v>
+        <v>965.8515168002863</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>949.6312043878088</v>
+        <v>949.1923389337295</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>933.7204567935134</v>
+        <v>933.3017758679387</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>918.5392193525583</v>
+        <v>918.1396711930283</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>904.0495775007878</v>
+        <v>903.6681704905612</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>890.2157796677624</v>
+        <v>889.8515786156751</v>
       </c>
     </row>
     <row r="8">
@@ -1203,25 +1203,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>1008.750073152542</v>
+        <v>1008.235608839452</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>990.1064967363387</v>
+        <v>989.6161275224034</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>972.3334486342604</v>
+        <v>971.865901705164</v>
       </c>
       <c r="E8" s="53" t="n">
-        <v>955.3850615818997</v>
+        <v>954.9391377731304</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>939.2181160344098</v>
+        <v>938.7926852262883</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>923.7918749975577</v>
+        <v>923.3858718187773</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>909.067929899094</v>
+        <v>908.6803497167407</v>
       </c>
     </row>
     <row r="9">
@@ -1229,25 +1229,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>1033.695574911236</v>
+        <v>1033.149296880565</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>1013.901310795978</v>
+        <v>1013.380738244521</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>995.035692880712</v>
+        <v>994.5394644765988</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>977.049666370286</v>
+        <v>976.5764996783223</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>959.8970127162612</v>
+        <v>959.4456992595481</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>943.5341724943273</v>
+        <v>943.1035731469934</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>927.9200801304254</v>
+        <v>927.5091208178063</v>
       </c>
     </row>
     <row r="10">
@@ -1255,25 +1255,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1058.641076669929</v>
+        <v>1058.062984921679</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>1037.696124855618</v>
+        <v>1037.145348966638</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>1017.737937127163</v>
+        <v>1017.213027248033</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>998.7142711586722</v>
+        <v>998.213861583514</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>980.5759093981128</v>
+        <v>980.0987132928079</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>963.2764699910971</v>
+        <v>962.8212744752093</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>946.772230361757</v>
+        <v>946.3378919188718</v>
       </c>
     </row>
     <row r="11">
@@ -1281,25 +1281,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>1083.586578428622</v>
+        <v>1082.976672962793</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>1061.490938915257</v>
+        <v>1060.909959688755</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>1040.440181373615</v>
+        <v>1039.886590019468</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>1020.378875947058</v>
+        <v>1019.851223488706</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>1001.254806079964</v>
+        <v>1000.751727326068</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>983.018767487867</v>
+        <v>982.5389758034253</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>965.6243805930885</v>
+        <v>965.1666630199375</v>
       </c>
     </row>
     <row r="13">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="B13" s="54" t="n">
-        <v>334.4700012207031</v>
+        <v>338.25</v>
       </c>
     </row>
     <row r="14">
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.07124403911248081</v>
+        <v>0.07137883953124738</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>12</v>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>1.023725768415924</v>
+        <v>1.023730478931415</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24404,7 +24404,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>334.4700012207031</v>
+        <v>338.25</v>
       </c>
     </row>
     <row r="49">
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>955.3850615818997</v>
+        <v>954.9391377731304</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>1117.023508541809</v>
+        <v>1116.391374795091</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>834.5288072283156</v>
+        <v>834.2197524575545</v>
       </c>
     </row>
     <row r="59">
